--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,19 +11,1039 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>Pharma</t>
-  </si>
-  <si>
-    <t>Ankit Jain</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="342">
+  <si>
+    <t>CSIS</t>
+  </si>
+  <si>
+    <t>A Michael Alphonse</t>
+  </si>
+  <si>
+    <t>Abhishek Mishra</t>
+  </si>
+  <si>
+    <t>Akanksha Bharadwaj</t>
+  </si>
+  <si>
+    <t>Akshaya Ganesan</t>
+  </si>
+  <si>
+    <t>Amit Dua</t>
+  </si>
+  <si>
+    <t>Anindya Neogi</t>
+  </si>
+  <si>
+    <t>Anita Ramachandran</t>
+  </si>
+  <si>
+    <t>Ankur Pachauri</t>
+  </si>
+  <si>
+    <t>Ashish Narang</t>
+  </si>
+  <si>
+    <t>Ashutosh Bhatia</t>
+  </si>
+  <si>
+    <t>Asish Bera</t>
+  </si>
+  <si>
+    <t>Avinash Gautam</t>
+  </si>
+  <si>
+    <t>Chandra Shekar R K</t>
+  </si>
+  <si>
+    <t>Chennupati Rakesh Prasanna</t>
+  </si>
+  <si>
+    <t>Dhruv Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Bharat Richhariya</t>
+  </si>
+  <si>
+    <t>Dr. Chetana Gavankar</t>
+  </si>
+  <si>
+    <t>Dr. Eht E Sham</t>
+  </si>
+  <si>
+    <t>Dr. Navneet Goyal</t>
+  </si>
+  <si>
+    <t>Dr. Ritu Arora</t>
+  </si>
+  <si>
+    <t>Dr. Shreyas Suresh Rao</t>
+  </si>
+  <si>
+    <t>Dr. Vijayalakshmi Anand</t>
+  </si>
+  <si>
+    <t>Febin a Vahab</t>
+  </si>
+  <si>
+    <t>G Venkiteswaran</t>
+  </si>
+  <si>
+    <t>Garima Jindal</t>
+  </si>
+  <si>
+    <t>Gopal Singh Phartiyal</t>
+  </si>
+  <si>
+    <t>Hari Babu K</t>
+  </si>
+  <si>
+    <t>Harish Kumar Aggarwal</t>
+  </si>
+  <si>
+    <t>Jagat Sesh Challa</t>
+  </si>
+  <si>
+    <t>Jyotsana Grover</t>
+  </si>
+  <si>
+    <t>K Venkatasubramanian</t>
+  </si>
+  <si>
+    <t>L. Rajya Lakshmi</t>
+  </si>
+  <si>
+    <t>Lucy J. Gudino</t>
+  </si>
+  <si>
+    <t>Mohammed Saleem J Bagewadi</t>
+  </si>
+  <si>
+    <t>Monali Tushar Mavani</t>
+  </si>
+  <si>
+    <t>Mrityunjay Kumar</t>
+  </si>
+  <si>
+    <t>Neha Vinayak</t>
+  </si>
+  <si>
+    <t>Nishit Narang</t>
+  </si>
+  <si>
+    <t>Pradheep Kumar K</t>
+  </si>
+  <si>
+    <t>Pranjal Vyas</t>
+  </si>
+  <si>
+    <t>Prashant Trivedi</t>
+  </si>
+  <si>
+    <t>Pratik Narang</t>
+  </si>
+  <si>
+    <t>Pravin Yashwant Pawar</t>
+  </si>
+  <si>
+    <t>Preethi N. G</t>
+  </si>
+  <si>
+    <t>Prof. J. P. Misra</t>
+  </si>
+  <si>
+    <t>Prof. Mukesh Kumar Rohil</t>
+  </si>
+  <si>
+    <t>Prof. Poonam Goyal</t>
+  </si>
+  <si>
+    <t>Raja Vadhana P</t>
+  </si>
+  <si>
+    <t>Rajesh Kumar</t>
+  </si>
+  <si>
+    <t>Rakhi Agrawal</t>
+  </si>
+  <si>
+    <t>Ramakrishna Dantu</t>
+  </si>
+  <si>
+    <t>Reddy Rani Vangimalla</t>
+  </si>
+  <si>
+    <t>Saikishor Jangiti</t>
+  </si>
+  <si>
+    <t>Sangeetha Vishwanathan</t>
+  </si>
+  <si>
+    <t>Seetha Parameswaran</t>
+  </si>
+  <si>
+    <t>Shashank Gupta</t>
+  </si>
+  <si>
+    <t>Sonika Chandrakant Rathi</t>
+  </si>
+  <si>
+    <t>Srinath Naidu</t>
+  </si>
+  <si>
+    <t>Sugata Ghosal</t>
+  </si>
+  <si>
+    <t>Sundaresan Raman</t>
+  </si>
+  <si>
+    <t>Swarna Chaudhary</t>
+  </si>
+  <si>
+    <t>T Venkateswara Rao</t>
+  </si>
+  <si>
+    <t>Tanmaya Mahapatra</t>
+  </si>
+  <si>
+    <t>Tejasvi Alladi</t>
+  </si>
+  <si>
+    <t>Veena Prabhakaran</t>
+  </si>
+  <si>
+    <t>Venkata Krishna Shashank Dara</t>
+  </si>
+  <si>
+    <t>Vimal S P</t>
+  </si>
+  <si>
+    <t>Vineet Kumar Garg</t>
+  </si>
+  <si>
+    <t>Vinti Agarwal</t>
+  </si>
+  <si>
+    <t>Virendra S Shekhawat</t>
+  </si>
+  <si>
+    <t>Vishal Gupta</t>
+  </si>
+  <si>
+    <t>Y V Ravi Kumar</t>
+  </si>
+  <si>
+    <t>Yash Sinha</t>
+  </si>
+  <si>
+    <t>Yashvardhan Sharma</t>
+  </si>
+  <si>
+    <t>Bio</t>
+  </si>
+  <si>
+    <t>Dr. Shashi Prakash Singh</t>
+  </si>
+  <si>
+    <t>Jigneshkumar Dahyabhai Prajapati</t>
+  </si>
+  <si>
+    <t>Jitendra Panwar</t>
+  </si>
+  <si>
+    <t>Meghana Tare</t>
+  </si>
+  <si>
+    <t>Mukul Joshi</t>
+  </si>
+  <si>
+    <t>P. R. Deepa</t>
+  </si>
+  <si>
+    <t>P. Yadukrishnan</t>
+  </si>
+  <si>
+    <t>Pankaj Kumar Sharma</t>
+  </si>
+  <si>
+    <t>Prabhat N. Jha</t>
+  </si>
+  <si>
+    <t>Prof. Ashis Kumar Das</t>
+  </si>
+  <si>
+    <t>Rajdeep Chowdhury</t>
+  </si>
+  <si>
+    <t>Sandhya Marathe</t>
+  </si>
+  <si>
+    <t>Shibasish Chowdhury</t>
+  </si>
+  <si>
+    <t>Shilpi Garg</t>
+  </si>
+  <si>
+    <t>SK Verma</t>
+  </si>
+  <si>
+    <t>Soumitra Ghosh</t>
+  </si>
+  <si>
+    <t>Sudeshna M Chowdhury</t>
+  </si>
+  <si>
+    <t>Sushmita Basu</t>
+  </si>
+  <si>
+    <t>Syamantak Majumder</t>
+  </si>
+  <si>
+    <t>Vani B.</t>
+  </si>
+  <si>
+    <t>Vishal Saxena</t>
+  </si>
+  <si>
+    <t>Phy</t>
+  </si>
+  <si>
+    <t>Anshuman Dalvi</t>
+  </si>
+  <si>
+    <t>Aritra Banerjee</t>
+  </si>
+  <si>
+    <t>Bhavesh Chauhan</t>
+  </si>
+  <si>
+    <t>Biswanath Layek</t>
+  </si>
+  <si>
+    <t>Dr. Amol R. Holkundkar</t>
+  </si>
+  <si>
+    <t>Dr. Arpan Das</t>
+  </si>
+  <si>
+    <t>Dr. D. D. Pant</t>
+  </si>
+  <si>
+    <t>Dr. Jayendra Nath Bandopadhyay</t>
+  </si>
+  <si>
+    <t>Dr. Kaushar Vaidya</t>
+  </si>
+  <si>
+    <t>Dr. Manjuladevi V</t>
+  </si>
+  <si>
+    <t>Dr R R Mishra</t>
+  </si>
+  <si>
+    <t>Dr. Rishikesh Vaidya</t>
+  </si>
+  <si>
+    <t>Dr. Sandipan Dutta</t>
+  </si>
+  <si>
+    <t>Dr. Subhashis Gangopadhyay</t>
+  </si>
+  <si>
+    <t>Dr. Tanmoy Mondal</t>
+  </si>
+  <si>
+    <t>Dr. Tapomoy Guha Sarkar</t>
+  </si>
+  <si>
+    <t>Navin Singh</t>
+  </si>
+  <si>
+    <t>Niladri Sarkar</t>
+  </si>
+  <si>
+    <t>Prof. Madhukar Mishra</t>
+  </si>
+  <si>
+    <t>Prof. Rakesh Choubisa</t>
+  </si>
+  <si>
+    <t>Prof S. Sindhu</t>
+  </si>
+  <si>
+    <t>Prof. Debashis Bandyopadhyay</t>
+  </si>
+  <si>
+    <t>Raj Kumar Gupta</t>
+  </si>
+  <si>
+    <t>Sajal Mukherjee</t>
+  </si>
+  <si>
+    <t>Srijata Dey</t>
+  </si>
+  <si>
+    <t>EEE</t>
+  </si>
+  <si>
+    <t>Shubha Sharma</t>
+  </si>
+  <si>
+    <t>Swapna S Kulkarni</t>
+  </si>
+  <si>
+    <t>Tanmay Ramesh Chaudhari</t>
+  </si>
+  <si>
+    <t>Thangella Pally Swapna</t>
+  </si>
+  <si>
+    <t>Dr. Vinay Chamola</t>
+  </si>
+  <si>
+    <t>Prof. Sainath Bitragunta</t>
+  </si>
+  <si>
+    <t>Prof. Satyendra Kumar Mourya</t>
+  </si>
+  <si>
+    <t>Prof. Suparna Chakraborty</t>
+  </si>
+  <si>
+    <t>Prof. V. Ramgopal Rao</t>
+  </si>
+  <si>
+    <t>Rajesh Kumar Tiwary</t>
+  </si>
+  <si>
+    <t>Ramesh Sambangi</t>
+  </si>
+  <si>
+    <t>Rekha A</t>
+  </si>
+  <si>
+    <t>Sandeep Joshi</t>
+  </si>
+  <si>
+    <t>Sanju Sharma</t>
+  </si>
+  <si>
+    <t>Sathisha Shet K</t>
+  </si>
+  <si>
+    <t>Satya Sudhakar Yedlapalli</t>
+  </si>
+  <si>
+    <t>Saurabh Gandhi</t>
+  </si>
+  <si>
+    <t>Dr. Shree Prasad M</t>
+  </si>
+  <si>
+    <t>Dr. Sujan Yenuganti</t>
+  </si>
+  <si>
+    <t>Dr. Syed Mohammad Zafaruddin</t>
+  </si>
+  <si>
+    <t>Dr. Vinod Kumar Chaubey</t>
+  </si>
+  <si>
+    <t>Gopala Krishna Koneru</t>
+  </si>
+  <si>
+    <t>Kranthi Kumar Palavalasa</t>
+  </si>
+  <si>
+    <t>Madhuri Bayya</t>
+  </si>
+  <si>
+    <t>Manoj Subhash Kakade</t>
+  </si>
+  <si>
+    <t>Neeraj Mishra</t>
+  </si>
+  <si>
+    <t>Parijanya Taragani</t>
+  </si>
+  <si>
+    <t>Pawan Sharma</t>
+  </si>
+  <si>
+    <t>Prof. Navneet Gupta</t>
+  </si>
+  <si>
+    <t>Dr. Meetha V. Shenoy</t>
+  </si>
+  <si>
+    <t>Dr. Nitin Chaturvedi</t>
+  </si>
+  <si>
+    <t>Dr. Pankaj Arora</t>
+  </si>
+  <si>
+    <t>Dr. Pawan Kamalakar Ajmera</t>
+  </si>
+  <si>
+    <t>Dr. Prashant Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Praveen Kumar A V</t>
+  </si>
+  <si>
+    <t>Dr. Puneet Mishra</t>
+  </si>
+  <si>
+    <t>Dr. Rahul Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Rahul Singhal</t>
+  </si>
+  <si>
+    <t>Dr. Rajneesh Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Sanjay Vidhyadharan</t>
+  </si>
+  <si>
+    <t>Dr. Sharda Tripathi</t>
+  </si>
+  <si>
+    <t>Dinesh Rane</t>
+  </si>
+  <si>
+    <t>Dr. Abhijit Rameshwar Asati</t>
+  </si>
+  <si>
+    <t>Dr. Aditya R. Gautam</t>
+  </si>
+  <si>
+    <t>Dr. Anu Gupta</t>
+  </si>
+  <si>
+    <t>Dr. Aruna Hazra</t>
+  </si>
+  <si>
+    <t>Dr. Ashish Patel</t>
+  </si>
+  <si>
+    <t>Dr. Dheerendra Singh</t>
+  </si>
+  <si>
+    <t>Dr. G Sai Sesha Chalapathi</t>
+  </si>
+  <si>
+    <t>Dr. Govind Prasad</t>
+  </si>
+  <si>
+    <t>Dr. Hari Om Bansal</t>
+  </si>
+  <si>
+    <t>Dr. Hitesh Datt Mathur</t>
+  </si>
+  <si>
+    <t>Dr. Karunesh Kumar Gupta</t>
+  </si>
+  <si>
+    <t>Humanities</t>
+  </si>
+  <si>
+    <t>Dr. S K Choudhary</t>
+  </si>
+  <si>
+    <t>Dr. Sailaja Nandigama</t>
+  </si>
+  <si>
+    <t>Dr. Sangeeta Sharma</t>
+  </si>
+  <si>
+    <t>Dr. Sushila Shekhawat</t>
+  </si>
+  <si>
+    <t>Dr. Tanu Shukla</t>
+  </si>
+  <si>
+    <t>Dr. Veena Ramachandran</t>
+  </si>
+  <si>
+    <t>Dr. Virendra Singh Nirban</t>
+  </si>
+  <si>
+    <t>Natasha Hazarika</t>
+  </si>
+  <si>
+    <t>Shriya Raina</t>
+  </si>
+  <si>
+    <t>Susan Haris</t>
+  </si>
+  <si>
+    <t>Dr. Anupam Yadav</t>
+  </si>
+  <si>
+    <t>Dr. Chintalapalli Vijayakumar</t>
+  </si>
+  <si>
+    <t>Dr. Devika Sangwan</t>
+  </si>
+  <si>
+    <t>Dr. Gajendra Singh Chauhan</t>
+  </si>
+  <si>
+    <t>Dr. Harikrishnan Gopinadhan Nair</t>
+  </si>
+  <si>
+    <t>Dr. Hricha Rashmi</t>
+  </si>
+  <si>
+    <t>Dr. Kumar Neeraj Sachdev</t>
+  </si>
+  <si>
+    <t>Dr. Madhurima Das</t>
+  </si>
+  <si>
+    <t>Dr. Paul Mathew</t>
+  </si>
+  <si>
+    <t>Dr. Prateek</t>
+  </si>
+  <si>
+    <t>Dr. Pushp Lata</t>
+  </si>
+  <si>
+    <t>Dr. Rajneesh Choubisa</t>
+  </si>
+  <si>
+    <t>Eco</t>
+  </si>
+  <si>
+    <t>Prof. Rahul Arora</t>
+  </si>
+  <si>
+    <t>Shrabana Tripathi</t>
+  </si>
+  <si>
+    <t>Suruchi Shrimali</t>
+  </si>
+  <si>
+    <t>Aditya Sharma</t>
+  </si>
+  <si>
+    <t>Aprajita Pandey</t>
+  </si>
+  <si>
+    <t>Dr. Arun Kumar Giri</t>
+  </si>
+  <si>
+    <t>Dr. Arya Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Balakrushna Padhi</t>
+  </si>
+  <si>
+    <t>Dr. Byomakesh Debata</t>
+  </si>
+  <si>
+    <t>Dr. Debi Prasad Bal</t>
+  </si>
+  <si>
+    <t>Dr. Geetilaxmi Mohapatra</t>
+  </si>
+  <si>
+    <t>Dr. Krishna Muniyoor</t>
+  </si>
+  <si>
+    <t>Dr. NV Muralidhar Rao</t>
+  </si>
+  <si>
+    <t>Dr. Rajan Pandey</t>
+  </si>
+  <si>
+    <t>Jyoti Dua</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>Divyum Sharma</t>
+  </si>
+  <si>
+    <t>Rahul Kumar</t>
+  </si>
+  <si>
+    <t>Niladri Chatterjee</t>
+  </si>
+  <si>
+    <t>Pramod Eyyunni</t>
+  </si>
+  <si>
+    <t>Rakhee</t>
+  </si>
+  <si>
+    <t>Rijubrata Kundu</t>
+  </si>
+  <si>
+    <t>Sangita Yadav</t>
+  </si>
+  <si>
+    <t>Shailesh Trivedi</t>
+  </si>
+  <si>
+    <t>Shivi Agarwal</t>
+  </si>
+  <si>
+    <t>Shuchita Goyal</t>
+  </si>
+  <si>
+    <t>Sudarshan Santra</t>
+  </si>
+  <si>
+    <t>Sumanta Pasari</t>
+  </si>
+  <si>
+    <t>Trilok Mathur</t>
+  </si>
+  <si>
+    <t>Anirudh Singh Rana</t>
+  </si>
+  <si>
+    <t>Ankan Pal</t>
+  </si>
+  <si>
+    <t>Ashish Tiwari</t>
+  </si>
+  <si>
+    <t>Balram Dubey</t>
+  </si>
+  <si>
+    <t>Chandra Shekhar</t>
+  </si>
+  <si>
+    <t>Deepak Bhoriya</t>
+  </si>
+  <si>
+    <t>Devendra Kumar</t>
+  </si>
+  <si>
+    <t>Dhiraj Kumar Das</t>
+  </si>
+  <si>
+    <t>Dr. Bhupendra Kumar Sharma</t>
+  </si>
+  <si>
+    <t>Gaurav Dwivedi</t>
+  </si>
+  <si>
+    <t>Jitender Kumar</t>
+  </si>
+  <si>
+    <t>Krishnendra Shekhawat</t>
+  </si>
+  <si>
+    <t>Mech</t>
+  </si>
+  <si>
+    <t>Prof. Kuldip Singh Sangwan</t>
+  </si>
+  <si>
+    <t>Prof. Mani Sankar Dasgupta</t>
+  </si>
+  <si>
+    <t>Prof. Chennu Ranganayakulu</t>
+  </si>
+  <si>
+    <t>Prof. Bijay Kumar Rout</t>
+  </si>
+  <si>
+    <t>Prof. Rajesh Prasad Mishra</t>
+  </si>
+  <si>
+    <t>Prof. Abhijeet Keshaorao Digalwar</t>
+  </si>
+  <si>
+    <t>Prof. Manoj Kumar Soni</t>
+  </si>
+  <si>
+    <t>Prof. Tufan Chandra Bera</t>
+  </si>
+  <si>
+    <t>Prof. Srikanta Routroy</t>
+  </si>
+  <si>
+    <t>Prof. P. Srinivasan</t>
+  </si>
+  <si>
+    <t>Prof. N.V.M. Rao</t>
+  </si>
+  <si>
+    <t>Prof. Shamsher Bahadur Singh</t>
+  </si>
+  <si>
+    <t>Prof. Ajit Pratap Singh</t>
+  </si>
+  <si>
+    <t>Prof. Arya Kumar</t>
+  </si>
+  <si>
+    <t>Prof. Annapoorna Gopal</t>
+  </si>
+  <si>
+    <t>Dr. Arun Kumar Jalan</t>
+  </si>
+  <si>
+    <t>Dr. Venkatesh Kadbur Prabhakar Rao</t>
+  </si>
+  <si>
+    <t>Dr. A. R. Harikrishnan</t>
+  </si>
+  <si>
+    <t>Dr. Gaurav Watts</t>
+  </si>
+  <si>
+    <t>Dr. Suvanjan Bhattacharyya</t>
+  </si>
+  <si>
+    <t>Dr. Tribeni Roy</t>
+  </si>
+  <si>
+    <t>Dr. Sharad Shrivastava</t>
+  </si>
+  <si>
+    <t>Dr. Sachin U. Belgamwar</t>
+  </si>
+  <si>
+    <t>Dr. Girish Kant</t>
+  </si>
+  <si>
+    <t>Dr. Shyam Sunder Yadav</t>
+  </si>
+  <si>
+    <t>Dr. Prateek Kala</t>
+  </si>
+  <si>
+    <t>Dr. Radha Raman Mishra</t>
+  </si>
+  <si>
+    <t>Dr. Murali Palla</t>
+  </si>
+  <si>
+    <t>Dr. Md. Qaisar Raza</t>
+  </si>
+  <si>
+    <t>Dr. Saket Verma</t>
+  </si>
+  <si>
+    <t>Dr. Aneesh A. M.</t>
+  </si>
+  <si>
+    <t>Dr. Amit Rajnarayan Singh</t>
+  </si>
+  <si>
+    <t>Dr. Aakash Chand Rai</t>
+  </si>
+  <si>
+    <t>Dr. Faizan Mohammad Rashid</t>
+  </si>
+  <si>
+    <t>Dr. Harpreet Singh Bedi</t>
+  </si>
+  <si>
+    <t>Dr. Majid Hassan Khan</t>
+  </si>
+  <si>
+    <t>Dr. Priyank Upadhyaya</t>
+  </si>
+  <si>
+    <t>Dr. Girish Kant Garg</t>
+  </si>
+  <si>
+    <t>Dr. Gulshan Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Geeta Bhatt</t>
+  </si>
+  <si>
+    <t>Dr. Anuj Sharma</t>
+  </si>
+  <si>
+    <t>Dr. Divyansh Patel</t>
+  </si>
+  <si>
+    <t>Dr. Srikanta Routroy</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>Prof. Shibani khanra jha</t>
+  </si>
+  <si>
+    <t>Prof. Dipendu Bhunia</t>
+  </si>
+  <si>
+    <t>Pubali Mandal</t>
+  </si>
+  <si>
+    <t>D. Sayantan Chakraborty</t>
+  </si>
+  <si>
+    <t>Prof. Kamalesh Kumar</t>
+  </si>
+  <si>
+    <t>Dr G Muthutkumar</t>
+  </si>
+  <si>
+    <t>Prof. Manoj kumar</t>
+  </si>
+  <si>
+    <t>Chemical</t>
+  </si>
+  <si>
+    <t>Dr Mohit Garg</t>
+  </si>
+  <si>
+    <t>Dr. Jay Pandey</t>
+  </si>
+  <si>
+    <t>Dr Bhanu Vardhan Reddy Kuncharam</t>
+  </si>
+  <si>
+    <t>Dr. Suresh Gupta</t>
+  </si>
+  <si>
+    <t>Dr. Banasri Roy</t>
+  </si>
+  <si>
+    <t>Dr. Hare Krishna Mohanta</t>
+  </si>
+  <si>
+    <t>Dr. Amit Jain</t>
+  </si>
+  <si>
+    <t>Dr. Smita Raghuvanshi</t>
+  </si>
+  <si>
+    <t>Dr. Krishna C. Etika</t>
+  </si>
+  <si>
+    <t>Dr. Ajaya Kumar Pani</t>
+  </si>
+  <si>
+    <t>Chemistry</t>
+  </si>
+  <si>
+    <t>Dr.Avik Kumar Pati</t>
+  </si>
+  <si>
+    <t>Dr. Bibhas Ranjan Sarkar</t>
+  </si>
+  <si>
+    <t>Dr. Dalip Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Shamik Chakraborty</t>
+  </si>
+  <si>
+    <t>Dr. Anil kumar</t>
+  </si>
+  <si>
+    <t>Dr. Inamur Rahaman Laskar</t>
+  </si>
+  <si>
+    <t>Dr. Madhushree Sarkar</t>
+  </si>
+  <si>
+    <t>Dr. Pritam Kumar Jana</t>
+  </si>
+  <si>
+    <t>Dr. Surojit Pande</t>
+  </si>
+  <si>
+    <t>Dr. Ajay Kumar Sah</t>
+  </si>
+  <si>
+    <t>Dr. Anish Rao</t>
+  </si>
+  <si>
+    <t>Dr. Indresh Kumar</t>
+  </si>
+  <si>
+    <t>Dr. Rajeev Sukheja</t>
+  </si>
+  <si>
+    <t>RMIT</t>
+  </si>
+  <si>
+    <t>Dr. Aneesh A. M</t>
+  </si>
+  <si>
+    <t>A R Harikirshnan</t>
+  </si>
+  <si>
+    <t>Dr. Madhurjya Dev Choudhury</t>
+  </si>
+  <si>
+    <t>Anuj Shamra</t>
+  </si>
+  <si>
+    <t>Prof. Shibani Khanra Jha</t>
+  </si>
+  <si>
+    <t>Arun Kumar Jalan</t>
+  </si>
+  <si>
+    <t>Rajesh P Mishra</t>
+  </si>
+  <si>
+    <t>Dr. M.S. Das Gupta</t>
+  </si>
+  <si>
+    <t>Dr. P. Srinivasan</t>
+  </si>
+  <si>
+    <t>Dr. Sachin U Belgamwar</t>
+  </si>
+  <si>
+    <t>Hemant Sharma</t>
+  </si>
+  <si>
+    <t>Srinibas Tripathy</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>Dr. Debasmita Dey (doubt)</t>
+  </si>
+  <si>
+    <t>Saurabh Chadha</t>
+  </si>
+  <si>
+    <t>Satyendra K Sharma</t>
+  </si>
+  <si>
+    <t>Dr. Mrinmoyee Basu</t>
+  </si>
+  <si>
+    <t>Pabitra Biswas(doubt)</t>
+  </si>
+  <si>
+    <t>Praveen Goyal</t>
+  </si>
+  <si>
+    <t>Mohammad Faraz Naim</t>
+  </si>
+  <si>
+    <t>Jayashree Mahesh</t>
+  </si>
+  <si>
+    <t>Daitri Tiwary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -33,6 +1053,12 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF0E0E0E"/>
+      <name val="&quot;Nunito Sans&quot;"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,21 +1081,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -81,6 +1104,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -284,1275 +1311,1775 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="29.25"/>
+    <col customWidth="1" min="2" max="2" width="23.5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3"/>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2"/>
+      <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2"/>
+      <c r="B19" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2"/>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2"/>
+      <c r="B21" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2"/>
+      <c r="B24" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="2"/>
+      <c r="B25" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="2"/>
+      <c r="B27" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="2"/>
+      <c r="B28" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="2"/>
+      <c r="B29" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2"/>
+      <c r="B30" s="2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="2"/>
+      <c r="B31" s="2" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="2"/>
+      <c r="B34" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2"/>
+      <c r="B35" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="2"/>
+      <c r="B36" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="2"/>
+      <c r="B38" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="2"/>
+      <c r="B40" s="2" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="2"/>
+      <c r="B42" s="2" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="2"/>
+      <c r="B43" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2"/>
+      <c r="B44" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2"/>
+      <c r="B45" s="2" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="2"/>
+      <c r="B46" s="2" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="2"/>
+      <c r="B47" s="2" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="2"/>
+      <c r="B48" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="2"/>
+      <c r="B49" s="2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="2"/>
+      <c r="B50" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2"/>
+      <c r="B51" s="2" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="2"/>
+      <c r="B52" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="2"/>
+      <c r="B53" s="2" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="2"/>
+      <c r="B54" s="2" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="2"/>
+      <c r="B55" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="2"/>
+      <c r="B57" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="2"/>
+      <c r="B59" s="2" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="2"/>
+      <c r="B60" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="2"/>
+      <c r="B61" s="2" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="2"/>
+      <c r="B62" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" s="2"/>
+      <c r="B63" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" s="2"/>
+      <c r="B64" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="2"/>
+      <c r="B65" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="2"/>
+      <c r="B66" s="2" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="2"/>
+      <c r="B67" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="2"/>
+      <c r="B68" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="2"/>
+      <c r="B69" s="2" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" s="2"/>
+      <c r="B70" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" s="2"/>
+      <c r="B71" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="2"/>
+      <c r="B72" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" s="2"/>
+      <c r="B73" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" s="2"/>
+      <c r="B74" s="2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="2"/>
+      <c r="B75" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
     </row>
     <row r="77">
-      <c r="A77" s="2"/>
+      <c r="B77" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" s="2"/>
+      <c r="B78" s="2" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" s="2"/>
+      <c r="B79" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="2"/>
+      <c r="B80" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="2"/>
+      <c r="B81" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="2"/>
+      <c r="B82" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="2"/>
+      <c r="B83" s="2" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="2"/>
+      <c r="B84" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="2"/>
+      <c r="B85" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="2"/>
+      <c r="B86" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="2"/>
+      <c r="B87" s="2" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="2"/>
+      <c r="B88" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="2"/>
+      <c r="B89" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="2"/>
+      <c r="B90" s="2" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="2"/>
+      <c r="B91" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="2"/>
+      <c r="B92" s="2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="2"/>
+      <c r="B93" s="2" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="2"/>
+      <c r="B94" s="2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="2"/>
+      <c r="B95" s="2" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" s="2"/>
+      <c r="B96" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="2"/>
+      <c r="B97" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
     </row>
     <row r="100">
-      <c r="A100" s="2"/>
+      <c r="B100" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="2"/>
+      <c r="B101" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="2"/>
+      <c r="B102" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="2"/>
+      <c r="B103" s="2" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="2"/>
+      <c r="B104" s="2" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="2"/>
+      <c r="B105" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="2"/>
+      <c r="B106" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="2"/>
+      <c r="B107" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="2"/>
+      <c r="B108" s="2" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="2"/>
+      <c r="B109" s="2" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="4"/>
+      <c r="B110" s="2" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="2"/>
+      <c r="B111" s="2" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="2"/>
+      <c r="B112" s="2" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="2"/>
+      <c r="B113" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="2"/>
+      <c r="B114" s="2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="2"/>
+      <c r="B115" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="2"/>
+      <c r="B116" s="2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="2"/>
+      <c r="B117" s="2" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="2"/>
+      <c r="B118" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="2"/>
+      <c r="B119" s="2" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="2"/>
+      <c r="B120" s="2" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="2"/>
+      <c r="B121" s="2" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="2"/>
+      <c r="B122" s="2" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="2"/>
+      <c r="B123" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="2"/>
+      <c r="B124" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="2"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2"/>
+      <c r="B125" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="2"/>
+      <c r="B127" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="2"/>
+      <c r="B128" s="2" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="2"/>
+      <c r="B129" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="2"/>
+      <c r="B130" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="2"/>
+      <c r="B131" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="2"/>
+      <c r="B132" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="2"/>
+      <c r="B133" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="2"/>
+      <c r="B134" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="2"/>
+      <c r="B135" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="2"/>
+      <c r="B136" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="2"/>
+      <c r="B137" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="2"/>
+      <c r="B138" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="2"/>
+      <c r="B139" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="2"/>
+      <c r="B140" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="2"/>
+      <c r="B141" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="4"/>
+      <c r="B142" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="2"/>
+      <c r="B143" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="4"/>
+      <c r="B144" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="2"/>
+      <c r="B145" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="2"/>
+      <c r="B146" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="2"/>
+      <c r="B147" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="2"/>
+      <c r="B148" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="2"/>
+      <c r="B149" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="2"/>
+      <c r="B150" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="2"/>
+      <c r="B151" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="2"/>
+      <c r="B152" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="2"/>
+      <c r="B153" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="2"/>
+      <c r="B154" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="2"/>
+      <c r="B155" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="2"/>
+      <c r="B156" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="2"/>
+      <c r="B157" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="4"/>
+      <c r="B158" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="2"/>
+      <c r="B159" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="2"/>
+      <c r="B160" s="2" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="2"/>
+      <c r="B161" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="2"/>
+      <c r="B162" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="2"/>
+      <c r="B163" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="2"/>
+      <c r="B164" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="2"/>
+      <c r="B165" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="2"/>
+      <c r="B166" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="2"/>
+      <c r="B167" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="2"/>
+      <c r="B168" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="2"/>
+      <c r="B169" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="2"/>
+      <c r="B170" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="2"/>
+      <c r="B171" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="2"/>
+      <c r="B172" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="2"/>
+      <c r="B173" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="2"/>
+      <c r="B174" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="2"/>
+      <c r="B175" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="2"/>
+      <c r="B176" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="2"/>
+      <c r="B177" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="2"/>
+      <c r="B178" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="2"/>
+      <c r="B179" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="2"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="4"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2"/>
+      <c r="B180" s="2" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="2"/>
+      <c r="B183" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="2"/>
+      <c r="B184" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="2"/>
+      <c r="B185" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="2"/>
+      <c r="B186" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="187">
-      <c r="A187" s="2"/>
+      <c r="B187" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="188">
-      <c r="A188" s="2"/>
+      <c r="B188" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="2"/>
+      <c r="B189" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="190">
-      <c r="A190" s="2"/>
+      <c r="B190" s="2" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="191">
-      <c r="A191" s="2"/>
+      <c r="B191" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="192">
-      <c r="A192" s="2"/>
+      <c r="B192" s="2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="193">
-      <c r="A193" s="2"/>
+      <c r="B193" s="2" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="194">
-      <c r="A194" s="2"/>
+      <c r="B194" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="195">
-      <c r="A195" s="2"/>
+      <c r="B195" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="196">
-      <c r="A196" s="2"/>
+      <c r="B196" s="2" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="197">
-      <c r="A197" s="2"/>
+      <c r="B197" s="2" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="198">
-      <c r="A198" s="2"/>
+      <c r="B198" s="2" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="199">
-      <c r="A199" s="2"/>
+      <c r="B199" s="2" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="200">
-      <c r="A200" s="2"/>
+      <c r="B200" s="2" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="201">
-      <c r="A201" s="2"/>
+      <c r="B201" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="202">
-      <c r="A202" s="2"/>
+      <c r="B202" s="2" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="203">
-      <c r="A203" s="2"/>
+      <c r="B203" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="204">
-      <c r="A204" s="2"/>
+      <c r="B204" s="2" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="205">
-      <c r="A205" s="2"/>
+      <c r="B205" s="2" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="206">
-      <c r="A206" s="2"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="2"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="2"/>
+      <c r="B206" s="2" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="209">
-      <c r="A209" s="2"/>
+      <c r="B209" s="2" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="210">
-      <c r="A210" s="2"/>
+      <c r="B210" s="2" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="211">
-      <c r="A211" s="2"/>
+      <c r="B211" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="212">
-      <c r="A212" s="2"/>
+      <c r="B212" s="2" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="213">
-      <c r="A213" s="2"/>
+      <c r="B213" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="214">
-      <c r="A214" s="2"/>
+      <c r="B214" s="2" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="215">
-      <c r="A215" s="2"/>
+      <c r="B215" s="2" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="216">
-      <c r="A216" s="2"/>
+      <c r="B216" s="2" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="217">
-      <c r="A217" s="2"/>
+      <c r="B217" s="2" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="218">
-      <c r="A218" s="2"/>
+      <c r="B218" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="219">
-      <c r="A219" s="2"/>
+      <c r="B219" s="2" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="2"/>
+      <c r="B220" s="2" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="221">
-      <c r="A221" s="2"/>
+      <c r="B221" s="2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="222">
-      <c r="A222" s="2"/>
+      <c r="B222" s="2" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="223">
-      <c r="A223" s="2"/>
+      <c r="B223" s="2" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="224">
-      <c r="A224" s="2"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="2"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="2"/>
+      <c r="B224" s="2" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="227">
-      <c r="A227" s="2"/>
+      <c r="B227" s="2" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="228">
-      <c r="A228" s="2"/>
+      <c r="B228" s="2" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="229">
-      <c r="A229" s="2"/>
+      <c r="B229" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="230">
-      <c r="A230" s="2"/>
+      <c r="B230" s="2" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="231">
-      <c r="A231" s="2"/>
+      <c r="B231" s="2" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="232">
-      <c r="A232" s="2"/>
+      <c r="B232" s="2" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="233">
-      <c r="A233" s="2"/>
+      <c r="B233" s="2" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="234">
-      <c r="A234" s="2"/>
+      <c r="B234" s="2" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="235">
-      <c r="A235" s="2"/>
+      <c r="B235" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="236">
-      <c r="A236" s="2"/>
+      <c r="B236" s="2" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="237">
-      <c r="A237" s="2"/>
+      <c r="B237" s="2" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="238">
-      <c r="A238" s="2"/>
+      <c r="B238" s="2" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="239">
-      <c r="A239" s="2"/>
+      <c r="B239" s="2" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="240">
-      <c r="A240" s="2"/>
+      <c r="B240" s="2" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="241">
-      <c r="A241" s="2"/>
+      <c r="B241" s="2" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="242">
-      <c r="A242" s="2"/>
+      <c r="B242" s="2" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="2"/>
+      <c r="B243" s="2" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="244">
-      <c r="A244" s="2"/>
+      <c r="B244" s="2" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="245">
-      <c r="A245" s="2"/>
+      <c r="B245" s="2" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="246">
-      <c r="A246" s="2"/>
+      <c r="B246" s="2" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="247">
-      <c r="A247" s="2"/>
+      <c r="B247" s="2" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="248">
-      <c r="A248" s="2"/>
+      <c r="B248" s="2" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="249">
-      <c r="A249" s="2"/>
+      <c r="B249" s="2" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="250">
-      <c r="A250" s="2"/>
+      <c r="B250" s="2" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="251">
-      <c r="A251" s="2"/>
+      <c r="B251" s="2" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="252">
-      <c r="A252" s="2"/>
+      <c r="B252" s="2" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="253">
-      <c r="A253" s="2"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="2"/>
+      <c r="B253" s="2" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="255">
-      <c r="A255" s="2"/>
+      <c r="B255" s="2" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="256">
-      <c r="A256" s="2"/>
+      <c r="B256" s="2" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="257">
-      <c r="A257" s="2"/>
+      <c r="B257" s="2" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="258">
-      <c r="A258" s="2"/>
+      <c r="B258" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="259">
-      <c r="A259" s="2"/>
+      <c r="B259" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="260">
-      <c r="A260" s="2"/>
+      <c r="B260" s="2" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="261">
-      <c r="A261" s="2"/>
+      <c r="B261" s="2" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="262">
-      <c r="A262" s="2"/>
+      <c r="B262" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="263">
-      <c r="A263" s="2"/>
+      <c r="B263" s="2" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="264">
-      <c r="A264" s="2"/>
+      <c r="B264" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="265">
-      <c r="A265" s="2"/>
+      <c r="B265" s="2" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="266">
-      <c r="A266" s="2"/>
+      <c r="B266" s="2" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="267">
-      <c r="A267" s="2"/>
+      <c r="B267" s="2" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="268">
-      <c r="A268" s="2"/>
+      <c r="B268" s="2" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="269">
-      <c r="A269" s="2"/>
+      <c r="B269" s="2" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="270">
-      <c r="A270" s="2"/>
+      <c r="B270" s="2" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="271">
-      <c r="A271" s="2"/>
+      <c r="B271" s="2" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="272">
-      <c r="A272" s="2"/>
+      <c r="B272" s="2" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="273">
-      <c r="A273" s="2"/>
+      <c r="B273" s="2" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="274">
-      <c r="A274" s="2"/>
+      <c r="B274" s="2" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="2"/>
+      <c r="B275" s="2" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="276">
-      <c r="A276" s="2"/>
+      <c r="B276" s="2" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="277">
-      <c r="A277" s="2"/>
+      <c r="B277" s="2" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="278">
-      <c r="A278" s="2"/>
+      <c r="B278" s="2" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="279">
-      <c r="A279" s="2"/>
+      <c r="B279" s="2" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="280">
-      <c r="A280" s="2"/>
+      <c r="B280" s="2" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="281">
-      <c r="A281" s="2"/>
+      <c r="B281" s="2" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="282">
-      <c r="A282" s="2"/>
+      <c r="B282" s="2" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="283">
-      <c r="A283" s="2"/>
+      <c r="B283" s="2" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="284">
-      <c r="A284" s="2"/>
+      <c r="B284" s="2" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="285">
-      <c r="A285" s="2"/>
+      <c r="B285" s="2" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="286">
-      <c r="A286" s="2"/>
+      <c r="B286" s="2" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="287">
-      <c r="A287" s="2"/>
+      <c r="B287" s="2" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="288">
-      <c r="A288" s="2"/>
+      <c r="B288" s="2" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="289">
-      <c r="A289" s="2"/>
+      <c r="B289" s="2" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="290">
-      <c r="A290" s="2"/>
+      <c r="B290" s="2" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="291">
-      <c r="A291" s="2"/>
+      <c r="B291" s="2" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="292">
-      <c r="A292" s="2"/>
+      <c r="B292" s="2" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="293">
-      <c r="A293" s="2"/>
+      <c r="B293" s="2" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="294">
-      <c r="A294" s="2"/>
+      <c r="B294" s="2" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="295">
-      <c r="A295" s="2"/>
+      <c r="B295" s="2" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="296">
-      <c r="A296" s="2"/>
+      <c r="B296" s="2" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="297">
-      <c r="A297" s="2"/>
+      <c r="B297" s="2" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="298">
-      <c r="A298" s="2"/>
+      <c r="B298" s="2" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="299">
-      <c r="A299" s="2"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="2"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="2"/>
+      <c r="B299" s="2" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="302">
-      <c r="A302" s="2"/>
+      <c r="B302" s="2" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="303">
-      <c r="A303" s="2"/>
+      <c r="B303" s="2" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="304">
-      <c r="A304" s="2"/>
+      <c r="B304" s="2" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="305">
-      <c r="A305" s="2"/>
+      <c r="B305" s="2" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="306">
-      <c r="A306" s="2"/>
+      <c r="B306" s="2" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="307">
-      <c r="A307" s="2"/>
+      <c r="B307" s="2" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="308">
-      <c r="A308" s="2"/>
+      <c r="B308" s="2" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="309">
-      <c r="A309" s="2"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="2"/>
+      <c r="B309" s="2" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="311">
-      <c r="A311" s="2"/>
+      <c r="B311" s="2" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="312">
-      <c r="A312" s="2"/>
+      <c r="B312" s="2" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="313">
-      <c r="A313" s="2"/>
+      <c r="B313" s="2" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="314">
-      <c r="A314" s="2"/>
+      <c r="B314" s="2" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="315">
-      <c r="A315" s="2"/>
+      <c r="B315" s="2" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="316">
-      <c r="A316" s="2"/>
+      <c r="B316" s="2" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="317">
-      <c r="A317" s="2"/>
+      <c r="B317" s="2" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="318">
-      <c r="A318" s="2"/>
+      <c r="B318" s="2" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="319">
-      <c r="A319" s="2"/>
+      <c r="B319" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="320">
-      <c r="A320" s="2"/>
+      <c r="B320" s="2" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="321">
-      <c r="A321" s="2"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="2"/>
+      <c r="B321" s="2" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="323">
-      <c r="A323" s="2"/>
+      <c r="B323" s="2" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="324">
-      <c r="A324" s="2"/>
+      <c r="B324" s="2" t="s">
+        <v>306</v>
+      </c>
     </row>
     <row r="325">
-      <c r="A325" s="2"/>
+      <c r="B325" s="2" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="326">
-      <c r="A326" s="2"/>
+      <c r="B326" s="2" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="327">
-      <c r="A327" s="2"/>
+      <c r="B327" s="2" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="328">
-      <c r="A328" s="2"/>
+      <c r="B328" s="2" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="329">
-      <c r="A329" s="2"/>
+      <c r="B329" s="2" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="330">
-      <c r="A330" s="2"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="2"/>
+      <c r="B330" s="2" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="332">
-      <c r="A332" s="2"/>
+      <c r="B332" s="2" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="333">
-      <c r="A333" s="2"/>
+      <c r="B333" s="2" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="334">
-      <c r="A334" s="2"/>
+      <c r="B334" s="2" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="335">
-      <c r="A335" s="2"/>
+      <c r="B335" s="2" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="336">
-      <c r="A336" s="2"/>
+      <c r="B336" s="2" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="337">
-      <c r="A337" s="2"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="2"/>
+      <c r="B337" s="2" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="339">
-      <c r="A339" s="2"/>
+      <c r="B339" s="2" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="340">
-      <c r="A340" s="2"/>
+      <c r="B340" s="2" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="341">
-      <c r="A341" s="2"/>
+      <c r="B341" s="2" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="342">
-      <c r="A342" s="2"/>
+      <c r="B342" s="3" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="343">
-      <c r="A343" s="2"/>
+      <c r="B343" s="2" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="344">
-      <c r="A344" s="2"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="2"/>
+      <c r="B344" s="2" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="346">
-      <c r="A346" s="2"/>
+      <c r="B346" s="2" t="s">
+        <v>325</v>
+      </c>
     </row>
     <row r="347">
-      <c r="A347" s="2"/>
+      <c r="B347" s="3" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="348">
-      <c r="A348" s="2"/>
+      <c r="B348" s="2" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="349">
-      <c r="A349" s="2"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="2"/>
+      <c r="B349" s="2" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="351">
-      <c r="A351" s="2"/>
+      <c r="B351" s="2" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="352">
-      <c r="A352" s="2"/>
+      <c r="B352" s="2" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="353">
-      <c r="A353" s="2"/>
+      <c r="B353" s="2" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="354">
-      <c r="A354" s="2"/>
+      <c r="B354" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="355">
-      <c r="A355" s="2"/>
+      <c r="B355" s="2" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="356">
-      <c r="A356" s="2"/>
+      <c r="B356" s="2" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="357">
-      <c r="A357" s="2"/>
+      <c r="B357" s="2" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="358">
-      <c r="A358" s="2"/>
+      <c r="B358" s="2" t="s">
+        <v>331</v>
+      </c>
     </row>
     <row r="359">
-      <c r="A359" s="2"/>
+      <c r="B359" s="2" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="360">
-      <c r="A360" s="2"/>
-    </row>
-    <row r="361">
-      <c r="A361" s="2"/>
+      <c r="B360" s="2" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="362">
-      <c r="A362" s="2"/>
+      <c r="B362" s="2" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="363">
-      <c r="A363" s="2"/>
+      <c r="B363" s="2" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="364">
-      <c r="A364" s="2"/>
+      <c r="B364" s="2" t="s">
+        <v>334</v>
+      </c>
     </row>
     <row r="365">
-      <c r="A365" s="2"/>
+      <c r="B365" s="2" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="366">
-      <c r="A366" s="2"/>
+      <c r="B366" s="2" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="367">
-      <c r="A367" s="2"/>
+      <c r="B367" s="2" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="368">
-      <c r="A368" s="2"/>
+      <c r="B368" s="2" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="369">
-      <c r="A369" s="2"/>
+      <c r="B369" s="2" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="370">
-      <c r="A370" s="2"/>
+      <c r="B370" s="2" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="371">
-      <c r="A371" s="2"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="2"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="2"/>
-    </row>
-    <row r="374">
-      <c r="A374" s="2"/>
-    </row>
-    <row r="375">
-      <c r="A375" s="2"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="2"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="2"/>
-    </row>
-    <row r="378">
-      <c r="A378" s="2"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="2"/>
-    </row>
-    <row r="380">
-      <c r="A380" s="2"/>
-    </row>
-    <row r="381">
-      <c r="A381" s="2"/>
-    </row>
-    <row r="382">
-      <c r="A382" s="2"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="2"/>
-    </row>
-    <row r="384">
-      <c r="A384" s="2"/>
-    </row>
-    <row r="385">
-      <c r="A385" s="2"/>
-    </row>
-    <row r="386">
-      <c r="A386" s="2"/>
-    </row>
-    <row r="387">
-      <c r="A387" s="2"/>
-    </row>
-    <row r="388">
-      <c r="A388" s="2"/>
-    </row>
-    <row r="389">
-      <c r="A389" s="2"/>
-    </row>
-    <row r="390">
-      <c r="A390" s="2"/>
-    </row>
-    <row r="391">
-      <c r="A391" s="2"/>
-    </row>
-    <row r="392">
-      <c r="A392" s="2"/>
-    </row>
-    <row r="393">
-      <c r="A393" s="2"/>
-    </row>
-    <row r="394">
-      <c r="A394" s="2"/>
-    </row>
-    <row r="395">
-      <c r="A395" s="2"/>
-    </row>
-    <row r="396">
-      <c r="A396" s="2"/>
-    </row>
-    <row r="397">
-      <c r="A397" s="2"/>
-    </row>
-    <row r="398">
-      <c r="A398" s="2"/>
-    </row>
-    <row r="399">
-      <c r="A399" s="2"/>
-    </row>
-    <row r="400">
-      <c r="A400" s="2"/>
-    </row>
-    <row r="401">
-      <c r="A401" s="2"/>
-    </row>
-    <row r="402">
-      <c r="A402" s="2"/>
-    </row>
-    <row r="403">
-      <c r="A403" s="2"/>
-    </row>
-    <row r="404">
-      <c r="A404" s="2"/>
-    </row>
-    <row r="405">
-      <c r="A405" s="2"/>
-    </row>
-    <row r="406">
-      <c r="A406" s="2"/>
-    </row>
-    <row r="407">
-      <c r="A407" s="2"/>
-    </row>
-    <row r="408">
-      <c r="A408" s="2"/>
-    </row>
-    <row r="409">
-      <c r="A409" s="2"/>
-    </row>
-    <row r="410">
-      <c r="A410" s="2"/>
-    </row>
-    <row r="411">
-      <c r="A411" s="2"/>
-    </row>
-    <row r="412">
-      <c r="A412" s="2"/>
-    </row>
-    <row r="413">
-      <c r="A413" s="2"/>
-    </row>
-    <row r="414">
-      <c r="A414" s="2"/>
-    </row>
-    <row r="415">
-      <c r="A415" s="2"/>
-    </row>
-    <row r="416">
-      <c r="A416" s="2"/>
-    </row>
-    <row r="417">
-      <c r="A417" s="2"/>
-    </row>
-    <row r="418">
-      <c r="A418" s="2"/>
-    </row>
-    <row r="419">
-      <c r="A419" s="2"/>
-    </row>
-    <row r="420">
-      <c r="A420" s="2"/>
-    </row>
-    <row r="421">
-      <c r="A421" s="2"/>
+      <c r="B371" s="2" t="s">
+        <v>341</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -1081,12 +1081,9 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1311,1773 +1308,1772 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="23.5"/>
+    <col customWidth="1" min="1" max="1" width="23.5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="2" t="s">
+      <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="2" t="s">
+      <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="2" t="s">
+      <c r="A69" s="1" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="2" t="s">
+      <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="2" t="s">
+      <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="2" t="s">
+      <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="2" t="s">
+      <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="2" t="s">
+      <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="2" t="s">
+      <c r="A75" s="1" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="2"/>
+      <c r="A76" s="1"/>
     </row>
     <row r="77">
-      <c r="B77" s="2" t="s">
+      <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="2" t="s">
+      <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="2" t="s">
+      <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="2" t="s">
+      <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="2" t="s">
+      <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="2" t="s">
+      <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="2" t="s">
+      <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="2" t="s">
+      <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="2" t="s">
+      <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="2" t="s">
+      <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="2" t="s">
+      <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="2" t="s">
+      <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="2" t="s">
+      <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="2" t="s">
+      <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="2" t="s">
+      <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="2" t="s">
+      <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="2" t="s">
+      <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="2" t="s">
+      <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="2" t="s">
+      <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="2" t="s">
+      <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="2" t="s">
+      <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="2"/>
+      <c r="A99" s="1"/>
     </row>
     <row r="100">
-      <c r="B100" s="2" t="s">
+      <c r="A100" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="2" t="s">
+      <c r="A101" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="2" t="s">
+      <c r="A102" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="2" t="s">
+      <c r="A103" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="2" t="s">
+      <c r="A104" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="2" t="s">
+      <c r="A105" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="2" t="s">
+      <c r="A106" s="1" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="2" t="s">
+      <c r="A107" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="2" t="s">
+      <c r="A108" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="2" t="s">
+      <c r="A109" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="2" t="s">
+      <c r="A110" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="2" t="s">
+      <c r="A111" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="2" t="s">
+      <c r="A112" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="2" t="s">
+      <c r="A113" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="2" t="s">
+      <c r="A114" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="115">
-      <c r="B115" s="2" t="s">
+      <c r="A115" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="116">
-      <c r="B116" s="2" t="s">
+      <c r="A116" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="117">
-      <c r="B117" s="2" t="s">
+      <c r="A117" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="118">
-      <c r="B118" s="2" t="s">
+      <c r="A118" s="1" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="119">
-      <c r="B119" s="2" t="s">
+      <c r="A119" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="120">
-      <c r="B120" s="2" t="s">
+      <c r="A120" s="1" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="121">
-      <c r="B121" s="2" t="s">
+      <c r="A121" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="122">
-      <c r="B122" s="2" t="s">
+      <c r="A122" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="2" t="s">
+      <c r="A123" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="2" t="s">
+      <c r="A124" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="125">
-      <c r="B125" s="2" t="s">
+      <c r="A125" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="2" t="s">
+      <c r="A127" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="128">
-      <c r="B128" s="2" t="s">
+      <c r="A128" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="129">
-      <c r="B129" s="2" t="s">
+      <c r="A129" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="130">
-      <c r="B130" s="2" t="s">
+      <c r="A130" s="1" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="131">
-      <c r="B131" s="2" t="s">
+      <c r="A131" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="132">
-      <c r="B132" s="2" t="s">
+      <c r="A132" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="133">
-      <c r="B133" s="2" t="s">
+      <c r="A133" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="134">
-      <c r="B134" s="2" t="s">
+      <c r="A134" s="1" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="135">
-      <c r="B135" s="2" t="s">
+      <c r="A135" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="136">
-      <c r="B136" s="2" t="s">
+      <c r="A136" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="137">
-      <c r="B137" s="2" t="s">
+      <c r="A137" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="138">
-      <c r="B138" s="2" t="s">
+      <c r="A138" s="1" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="139">
-      <c r="B139" s="2" t="s">
+      <c r="A139" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="140">
-      <c r="B140" s="2" t="s">
+      <c r="A140" s="1" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="141">
-      <c r="B141" s="2" t="s">
+      <c r="A141" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="142">
-      <c r="B142" s="2" t="s">
+      <c r="A142" s="1" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="143">
-      <c r="B143" s="2" t="s">
+      <c r="A143" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="144">
-      <c r="B144" s="2" t="s">
+      <c r="A144" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="145">
-      <c r="B145" s="2" t="s">
+      <c r="A145" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="146">
-      <c r="B146" s="2" t="s">
+      <c r="A146" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="147">
-      <c r="B147" s="2" t="s">
+      <c r="A147" s="1" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="148">
-      <c r="B148" s="2" t="s">
+      <c r="A148" s="1" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="149">
-      <c r="B149" s="2" t="s">
+      <c r="A149" s="1" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="150">
-      <c r="B150" s="2" t="s">
+      <c r="A150" s="1" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="151">
-      <c r="B151" s="2" t="s">
+      <c r="A151" s="1" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="152">
-      <c r="B152" s="2" t="s">
+      <c r="A152" s="1" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="153">
-      <c r="B153" s="2" t="s">
+      <c r="A153" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="154">
-      <c r="B154" s="2" t="s">
+      <c r="A154" s="1" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="155">
-      <c r="B155" s="2" t="s">
+      <c r="A155" s="1" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="156">
-      <c r="B156" s="2" t="s">
+      <c r="A156" s="1" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="157">
-      <c r="B157" s="2" t="s">
+      <c r="A157" s="1" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="158">
-      <c r="B158" s="2" t="s">
+      <c r="A158" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="159">
-      <c r="B159" s="2" t="s">
+      <c r="A159" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="160">
-      <c r="B160" s="2" t="s">
+      <c r="A160" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="161">
-      <c r="B161" s="2" t="s">
+      <c r="A161" s="1" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="162">
-      <c r="B162" s="2" t="s">
+      <c r="A162" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="163">
-      <c r="B163" s="2" t="s">
+      <c r="A163" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="164">
-      <c r="B164" s="2" t="s">
+      <c r="A164" s="1" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="165">
-      <c r="B165" s="2" t="s">
+      <c r="A165" s="1" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="166">
-      <c r="B166" s="2" t="s">
+      <c r="A166" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="167">
-      <c r="B167" s="2" t="s">
+      <c r="A167" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="168">
-      <c r="B168" s="2" t="s">
+      <c r="A168" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="169">
-      <c r="B169" s="2" t="s">
+      <c r="A169" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="170">
-      <c r="B170" s="2" t="s">
+      <c r="A170" s="1" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="171">
-      <c r="B171" s="2" t="s">
+      <c r="A171" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="172">
-      <c r="B172" s="2" t="s">
+      <c r="A172" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="173">
-      <c r="B173" s="2" t="s">
+      <c r="A173" s="1" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="174">
-      <c r="B174" s="2" t="s">
+      <c r="A174" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="175">
-      <c r="B175" s="2" t="s">
+      <c r="A175" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="176">
-      <c r="B176" s="2" t="s">
+      <c r="A176" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="177">
-      <c r="B177" s="2" t="s">
+      <c r="A177" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="178">
-      <c r="B178" s="2" t="s">
+      <c r="A178" s="1" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="179">
-      <c r="B179" s="2" t="s">
+      <c r="A179" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="180">
-      <c r="B180" s="2" t="s">
+      <c r="A180" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="183">
-      <c r="B183" s="2" t="s">
+      <c r="A183" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="184">
-      <c r="B184" s="2" t="s">
+      <c r="A184" s="1" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="185">
-      <c r="B185" s="2" t="s">
+      <c r="A185" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="186">
-      <c r="B186" s="2" t="s">
+      <c r="A186" s="1" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="187">
-      <c r="B187" s="2" t="s">
+      <c r="A187" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="188">
-      <c r="B188" s="2" t="s">
+      <c r="A188" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="189">
-      <c r="B189" s="2" t="s">
+      <c r="A189" s="1" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="190">
-      <c r="B190" s="2" t="s">
+      <c r="A190" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="191">
-      <c r="B191" s="2" t="s">
+      <c r="A191" s="1" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="192">
-      <c r="B192" s="2" t="s">
+      <c r="A192" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="193">
-      <c r="B193" s="2" t="s">
+      <c r="A193" s="1" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="194">
-      <c r="B194" s="2" t="s">
+      <c r="A194" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="195">
-      <c r="B195" s="2" t="s">
+      <c r="A195" s="1" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="196">
-      <c r="B196" s="2" t="s">
+      <c r="A196" s="1" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="197">
-      <c r="B197" s="2" t="s">
+      <c r="A197" s="1" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="198">
-      <c r="B198" s="2" t="s">
+      <c r="A198" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="199">
-      <c r="B199" s="2" t="s">
+      <c r="A199" s="1" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="200">
-      <c r="B200" s="2" t="s">
+      <c r="A200" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="201">
-      <c r="B201" s="2" t="s">
+      <c r="A201" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="202">
-      <c r="B202" s="2" t="s">
+      <c r="A202" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="203">
-      <c r="B203" s="2" t="s">
+      <c r="A203" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="204">
-      <c r="B204" s="2" t="s">
+      <c r="A204" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="205">
-      <c r="B205" s="2" t="s">
+      <c r="A205" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="206">
-      <c r="B206" s="2" t="s">
+      <c r="A206" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="209">
-      <c r="B209" s="2" t="s">
+      <c r="A209" s="1" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="210">
-      <c r="B210" s="2" t="s">
+      <c r="A210" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="211">
-      <c r="B211" s="2" t="s">
+      <c r="A211" s="1" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="212">
-      <c r="B212" s="2" t="s">
+      <c r="A212" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="213">
-      <c r="B213" s="2" t="s">
+      <c r="A213" s="1" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="214">
-      <c r="B214" s="2" t="s">
+      <c r="A214" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="215">
-      <c r="B215" s="2" t="s">
+      <c r="A215" s="1" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="216">
-      <c r="B216" s="2" t="s">
+      <c r="A216" s="1" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="217">
-      <c r="B217" s="2" t="s">
+      <c r="A217" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="218">
-      <c r="B218" s="2" t="s">
+      <c r="A218" s="1" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="219">
-      <c r="B219" s="2" t="s">
+      <c r="A219" s="1" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="220">
-      <c r="B220" s="2" t="s">
+      <c r="A220" s="1" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="221">
-      <c r="B221" s="2" t="s">
+      <c r="A221" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="222">
-      <c r="B222" s="2" t="s">
+      <c r="A222" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="223">
-      <c r="B223" s="2" t="s">
+      <c r="A223" s="1" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="224">
-      <c r="B224" s="2" t="s">
+      <c r="A224" s="1" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="227">
-      <c r="B227" s="2" t="s">
+      <c r="A227" s="1" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="228">
-      <c r="B228" s="2" t="s">
+      <c r="A228" s="1" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="229">
-      <c r="B229" s="2" t="s">
+      <c r="A229" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="230">
-      <c r="B230" s="2" t="s">
+      <c r="A230" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="231">
-      <c r="B231" s="2" t="s">
+      <c r="A231" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="232">
-      <c r="B232" s="2" t="s">
+      <c r="A232" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="233">
-      <c r="B233" s="2" t="s">
+      <c r="A233" s="1" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="234">
-      <c r="B234" s="2" t="s">
+      <c r="A234" s="1" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="235">
-      <c r="B235" s="2" t="s">
+      <c r="A235" s="1" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="236">
-      <c r="B236" s="2" t="s">
+      <c r="A236" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="237">
-      <c r="B237" s="2" t="s">
+      <c r="A237" s="1" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="238">
-      <c r="B238" s="2" t="s">
+      <c r="A238" s="1" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="239">
-      <c r="B239" s="2" t="s">
+      <c r="A239" s="1" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="240">
-      <c r="B240" s="2" t="s">
+      <c r="A240" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="241">
-      <c r="B241" s="2" t="s">
+      <c r="A241" s="1" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="242">
-      <c r="B242" s="2" t="s">
+      <c r="A242" s="1" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="243">
-      <c r="B243" s="2" t="s">
+      <c r="A243" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="244">
-      <c r="B244" s="2" t="s">
+      <c r="A244" s="1" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="245">
-      <c r="B245" s="2" t="s">
+      <c r="A245" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="246">
-      <c r="B246" s="2" t="s">
+      <c r="A246" s="1" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="247">
-      <c r="B247" s="2" t="s">
+      <c r="A247" s="1" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="248">
-      <c r="B248" s="2" t="s">
+      <c r="A248" s="1" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="249">
-      <c r="B249" s="2" t="s">
+      <c r="A249" s="1" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="250">
-      <c r="B250" s="2" t="s">
+      <c r="A250" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="251">
-      <c r="B251" s="2" t="s">
+      <c r="A251" s="1" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="252">
-      <c r="B252" s="2" t="s">
+      <c r="A252" s="1" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="253">
-      <c r="B253" s="2" t="s">
+      <c r="A253" s="1" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="255">
-      <c r="B255" s="2" t="s">
+      <c r="A255" s="1" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="256">
-      <c r="B256" s="2" t="s">
+      <c r="A256" s="1" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="257">
-      <c r="B257" s="2" t="s">
+      <c r="A257" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="258">
-      <c r="B258" s="2" t="s">
+      <c r="A258" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="259">
-      <c r="B259" s="2" t="s">
+      <c r="A259" s="1" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="260">
-      <c r="B260" s="2" t="s">
+      <c r="A260" s="1" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="261">
-      <c r="B261" s="2" t="s">
+      <c r="A261" s="1" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="262">
-      <c r="B262" s="2" t="s">
+      <c r="A262" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="263">
-      <c r="B263" s="2" t="s">
+      <c r="A263" s="1" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="264">
-      <c r="B264" s="2" t="s">
+      <c r="A264" s="1" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="265">
-      <c r="B265" s="2" t="s">
+      <c r="A265" s="1" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="266">
-      <c r="B266" s="2" t="s">
+      <c r="A266" s="1" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="267">
-      <c r="B267" s="2" t="s">
+      <c r="A267" s="1" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="268">
-      <c r="B268" s="2" t="s">
+      <c r="A268" s="1" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="269">
-      <c r="B269" s="2" t="s">
+      <c r="A269" s="1" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="270">
-      <c r="B270" s="2" t="s">
+      <c r="A270" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="271">
-      <c r="B271" s="2" t="s">
+      <c r="A271" s="1" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="272">
-      <c r="B272" s="2" t="s">
+      <c r="A272" s="1" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="273">
-      <c r="B273" s="2" t="s">
+      <c r="A273" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="274">
-      <c r="B274" s="2" t="s">
+      <c r="A274" s="1" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="275">
-      <c r="B275" s="2" t="s">
+      <c r="A275" s="1" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="276">
-      <c r="B276" s="2" t="s">
+      <c r="A276" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="277">
-      <c r="B277" s="2" t="s">
+      <c r="A277" s="1" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="278">
-      <c r="B278" s="2" t="s">
+      <c r="A278" s="1" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="279">
-      <c r="B279" s="2" t="s">
+      <c r="A279" s="1" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="280">
-      <c r="B280" s="2" t="s">
+      <c r="A280" s="1" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="281">
-      <c r="B281" s="2" t="s">
+      <c r="A281" s="1" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="282">
-      <c r="B282" s="2" t="s">
+      <c r="A282" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="283">
-      <c r="B283" s="2" t="s">
+      <c r="A283" s="1" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="284">
-      <c r="B284" s="2" t="s">
+      <c r="A284" s="1" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="285">
-      <c r="B285" s="2" t="s">
+      <c r="A285" s="1" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="286">
-      <c r="B286" s="2" t="s">
+      <c r="A286" s="1" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="287">
-      <c r="B287" s="2" t="s">
+      <c r="A287" s="1" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="288">
-      <c r="B288" s="2" t="s">
+      <c r="A288" s="1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="289">
-      <c r="B289" s="2" t="s">
+      <c r="A289" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="290">
-      <c r="B290" s="2" t="s">
+      <c r="A290" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="291">
-      <c r="B291" s="2" t="s">
+      <c r="A291" s="1" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="292">
-      <c r="B292" s="2" t="s">
+      <c r="A292" s="1" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="293">
-      <c r="B293" s="2" t="s">
+      <c r="A293" s="1" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="294">
-      <c r="B294" s="2" t="s">
+      <c r="A294" s="1" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="295">
-      <c r="B295" s="2" t="s">
+      <c r="A295" s="1" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="296">
-      <c r="B296" s="2" t="s">
+      <c r="A296" s="1" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="297">
-      <c r="B297" s="2" t="s">
+      <c r="A297" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="298">
-      <c r="B298" s="2" t="s">
+      <c r="A298" s="1" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="299">
-      <c r="B299" s="2" t="s">
+      <c r="A299" s="1" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="302">
-      <c r="B302" s="2" t="s">
+      <c r="A302" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="303">
-      <c r="B303" s="2" t="s">
+      <c r="A303" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="304">
-      <c r="B304" s="2" t="s">
+      <c r="A304" s="1" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="305">
-      <c r="B305" s="2" t="s">
+      <c r="A305" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="306">
-      <c r="B306" s="2" t="s">
+      <c r="A306" s="1" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="307">
-      <c r="B307" s="2" t="s">
+      <c r="A307" s="1" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="308">
-      <c r="B308" s="2" t="s">
+      <c r="A308" s="1" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="309">
-      <c r="B309" s="2" t="s">
+      <c r="A309" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="311">
-      <c r="B311" s="2" t="s">
+      <c r="A311" s="1" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="312">
-      <c r="B312" s="2" t="s">
+      <c r="A312" s="1" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="313">
-      <c r="B313" s="2" t="s">
+      <c r="A313" s="1" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="314">
-      <c r="B314" s="2" t="s">
+      <c r="A314" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="315">
-      <c r="B315" s="2" t="s">
+      <c r="A315" s="1" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="316">
-      <c r="B316" s="2" t="s">
+      <c r="A316" s="1" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="317">
-      <c r="B317" s="2" t="s">
+      <c r="A317" s="1" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="318">
-      <c r="B318" s="2" t="s">
+      <c r="A318" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="319">
-      <c r="B319" s="2" t="s">
+      <c r="A319" s="1" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="320">
-      <c r="B320" s="2" t="s">
+      <c r="A320" s="1" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="321">
-      <c r="B321" s="2" t="s">
+      <c r="A321" s="1" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="323">
-      <c r="B323" s="2" t="s">
+      <c r="A323" s="1" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="324">
-      <c r="B324" s="2" t="s">
+      <c r="A324" s="1" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="325">
-      <c r="B325" s="2" t="s">
+      <c r="A325" s="1" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="326">
-      <c r="B326" s="2" t="s">
+      <c r="A326" s="1" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="327">
-      <c r="B327" s="2" t="s">
+      <c r="A327" s="1" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="328">
-      <c r="B328" s="2" t="s">
+      <c r="A328" s="1" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="329">
-      <c r="B329" s="2" t="s">
+      <c r="A329" s="1" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="330">
-      <c r="B330" s="2" t="s">
+      <c r="A330" s="1" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="332">
-      <c r="B332" s="2" t="s">
+      <c r="A332" s="1" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="333">
-      <c r="B333" s="2" t="s">
+      <c r="A333" s="1" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="334">
-      <c r="B334" s="2" t="s">
+      <c r="A334" s="1" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="335">
-      <c r="B335" s="2" t="s">
+      <c r="A335" s="1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="336">
-      <c r="B336" s="2" t="s">
+      <c r="A336" s="1" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="337">
-      <c r="B337" s="2" t="s">
+      <c r="A337" s="1" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="339">
-      <c r="B339" s="2" t="s">
+      <c r="A339" s="1" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="340">
-      <c r="B340" s="2" t="s">
+      <c r="A340" s="1" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="341">
-      <c r="B341" s="2" t="s">
+      <c r="A341" s="1" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="342">
-      <c r="B342" s="3" t="s">
+      <c r="A342" s="2" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="343">
-      <c r="B343" s="2" t="s">
+      <c r="A343" s="1" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="344">
-      <c r="B344" s="2" t="s">
+      <c r="A344" s="1" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="346">
-      <c r="B346" s="2" t="s">
+      <c r="A346" s="1" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="347">
-      <c r="B347" s="3" t="s">
+      <c r="A347" s="2" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="348">
-      <c r="B348" s="2" t="s">
+      <c r="A348" s="1" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="349">
-      <c r="B349" s="2" t="s">
+      <c r="A349" s="1" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="351">
-      <c r="B351" s="2" t="s">
+      <c r="A351" s="1" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="352">
-      <c r="B352" s="2" t="s">
+      <c r="A352" s="1" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="353">
-      <c r="B353" s="2" t="s">
+      <c r="A353" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="354">
-      <c r="B354" s="2" t="s">
+      <c r="A354" s="1" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="355">
-      <c r="B355" s="2" t="s">
+      <c r="A355" s="1" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="356">
-      <c r="B356" s="2" t="s">
+      <c r="A356" s="1" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="357">
-      <c r="B357" s="2" t="s">
+      <c r="A357" s="1" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="358">
-      <c r="B358" s="2" t="s">
+      <c r="A358" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="359">
-      <c r="B359" s="2" t="s">
+      <c r="A359" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="360">
-      <c r="B360" s="2" t="s">
+      <c r="A360" s="1" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="362">
-      <c r="B362" s="2" t="s">
+      <c r="A362" s="1" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="363">
-      <c r="B363" s="2" t="s">
+      <c r="A363" s="1" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="364">
-      <c r="B364" s="2" t="s">
+      <c r="A364" s="1" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="365">
-      <c r="B365" s="2" t="s">
+      <c r="A365" s="1" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="366">
-      <c r="B366" s="2" t="s">
+      <c r="A366" s="1" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="367">
-      <c r="B367" s="2" t="s">
+      <c r="A367" s="1" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="368">
-      <c r="B368" s="2" t="s">
+      <c r="A368" s="1" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="369">
-      <c r="B369" s="2" t="s">
+      <c r="A369" s="1" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="370">
-      <c r="B370" s="2" t="s">
+      <c r="A370" s="1" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="371">
-      <c r="B371" s="2" t="s">
+      <c r="A371" s="1" t="s">
         <v>341</v>
       </c>
     </row>

--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="361">
   <si>
     <t>CSIS</t>
   </si>
@@ -1037,6 +1037,63 @@
   </si>
   <si>
     <t>Daitri Tiwary</t>
+  </si>
+  <si>
+    <t>Pharma</t>
+  </si>
+  <si>
+    <t>Bharathi R</t>
+  </si>
+  <si>
+    <t>Dr. Aniruddha Roy</t>
+  </si>
+  <si>
+    <t>Dr. Ankit Jain</t>
+  </si>
+  <si>
+    <t>Dr. Deepak Chitkara</t>
+  </si>
+  <si>
+    <t>Dr. Hemant R. Jadhav</t>
+  </si>
+  <si>
+    <t>Dr. Jagpreet Singh Sidhu</t>
+  </si>
+  <si>
+    <t>Dr. Murali Pandey</t>
+  </si>
+  <si>
+    <t>Dr. Paul Tulshiram</t>
+  </si>
+  <si>
+    <t>Dr. Pragyanshu Khare</t>
+  </si>
+  <si>
+    <t>Dr. Rajeev Taliyan</t>
+  </si>
+  <si>
+    <t>Dr. Richa Shrivastava</t>
+  </si>
+  <si>
+    <t>Dr. S Murugesan</t>
+  </si>
+  <si>
+    <t>Gautam Kumar</t>
+  </si>
+  <si>
+    <t>Gautam Singhvi</t>
+  </si>
+  <si>
+    <t>Prof. Gaikwad Bhandudas</t>
+  </si>
+  <si>
+    <t>Prof. R. Mahesh</t>
+  </si>
+  <si>
+    <t>Prof. Anil Jindal</t>
+  </si>
+  <si>
+    <t>Sandeep Sundriyal</t>
   </si>
 </sst>
 </file>
@@ -3077,6 +3134,101 @@
         <v>341</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="1" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="361">
   <si>
     <t>CSIS</t>
   </si>
@@ -1100,7 +1100,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1108,6 +1108,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -1138,14 +1144,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -2830,402 +2839,407 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="s">
-        <v>288</v>
+      <c r="A304" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="s">
         <v>293</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="s">
         <v>304</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="s">
         <v>312</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" s="2" t="s">
+    <row r="343">
+      <c r="A343" s="3" t="s">
         <v>322</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" s="1" t="s">
+    <row r="347">
+      <c r="A347" s="1" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" s="2" t="s">
+    <row r="348">
+      <c r="A348" s="3" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="1" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
-        <v>245</v>
+        <v>329</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
-        <v>330</v>
+        <v>269</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
-        <v>289</v>
+        <v>331</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="1" t="s">
         <v>290</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="1" t="s">
         <v>341</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="1" t="s">
         <v>360</v>
       </c>
     </row>

--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="362">
   <si>
     <t>CSIS</t>
   </si>
@@ -890,6 +890,9 @@
   </si>
   <si>
     <t>Dr G Muthutkumar</t>
+  </si>
+  <si>
+    <t>Prof. Anshuman</t>
   </si>
   <si>
     <t>Prof. Manoj kumar</t>
@@ -2873,8 +2876,8 @@
         <v>293</v>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="1" t="s">
+    <row r="311">
+      <c r="A311" s="1" t="s">
         <v>294</v>
       </c>
     </row>
@@ -2928,8 +2931,8 @@
         <v>304</v>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" s="1" t="s">
+    <row r="323">
+      <c r="A323" s="1" t="s">
         <v>305</v>
       </c>
     </row>
@@ -2968,8 +2971,8 @@
         <v>312</v>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" s="1" t="s">
+    <row r="332">
+      <c r="A332" s="1" t="s">
         <v>313</v>
       </c>
     </row>
@@ -2998,8 +3001,8 @@
         <v>318</v>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" s="1" t="s">
+    <row r="339">
+      <c r="A339" s="1" t="s">
         <v>319</v>
       </c>
     </row>
@@ -3014,12 +3017,12 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="3" t="s">
+      <c r="A343" s="1" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="s">
+      <c r="A344" s="3" t="s">
         <v>323</v>
       </c>
     </row>
@@ -3028,29 +3031,29 @@
         <v>324</v>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" s="1" t="s">
+    <row r="346">
+      <c r="A346" s="1" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="3" t="s">
+      <c r="A348" s="1" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="s">
+      <c r="A349" s="3" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="1" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="353">
@@ -3060,27 +3063,27 @@
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
-        <v>245</v>
+        <v>330</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
-        <v>269</v>
+        <v>294</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
-        <v>330</v>
+        <v>269</v>
       </c>
     </row>
     <row r="359">
@@ -3090,17 +3093,17 @@
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
-        <v>289</v>
+        <v>332</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="1" t="s">
         <v>290</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="364">
@@ -3148,8 +3151,8 @@
         <v>341</v>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" s="1" t="s">
+    <row r="373">
+      <c r="A373" s="1" t="s">
         <v>342</v>
       </c>
     </row>
@@ -3241,6 +3244,11 @@
     <row r="392">
       <c r="A392" s="1" t="s">
         <v>360</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="1" t="s">
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="362">
   <si>
     <t>CSIS</t>
   </si>
@@ -955,6 +955,9 @@
     <t>Dr. Madhushree Sarkar</t>
   </si>
   <si>
+    <t>Dr. Mrinmoyee Basu</t>
+  </si>
+  <si>
     <t>Dr. Pritam Kumar Jana</t>
   </si>
   <si>
@@ -1022,9 +1025,6 @@
   </si>
   <si>
     <t>Satyendra K Sharma</t>
-  </si>
-  <si>
-    <t>Dr. Mrinmoyee Basu</t>
   </si>
   <si>
     <t>Pabitra Biswas(doubt)</t>
@@ -2976,79 +2976,84 @@
         <v>313</v>
       </c>
     </row>
+    <row r="333">
+      <c r="A333" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
     <row r="334">
       <c r="A334" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="351">
@@ -3058,12 +3063,12 @@
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="355">
@@ -3088,12 +3093,12 @@
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="361">
@@ -3108,27 +3113,27 @@
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="s">
-        <v>337</v>
+        <v>314</v>
       </c>
     </row>
     <row r="369">

--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="362">
   <si>
     <t>CSIS</t>
   </si>
@@ -871,6 +871,18 @@
     <t>Dr. Srikanta Routroy</t>
   </si>
   <si>
+    <t>Dr. Madhurjya Dev Choudhury</t>
+  </si>
+  <si>
+    <t>Dr. M.S. Das Gupta</t>
+  </si>
+  <si>
+    <t>Hemant Sharma</t>
+  </si>
+  <si>
+    <t>Srinibas Tripathy</t>
+  </si>
+  <si>
     <t>Civil</t>
   </si>
   <si>
@@ -985,9 +997,6 @@
     <t>A R Harikirshnan</t>
   </si>
   <si>
-    <t>Dr. Madhurjya Dev Choudhury</t>
-  </si>
-  <si>
     <t>Anuj Shamra</t>
   </si>
   <si>
@@ -1000,19 +1009,10 @@
     <t>Rajesh P Mishra</t>
   </si>
   <si>
-    <t>Dr. M.S. Das Gupta</t>
-  </si>
-  <si>
     <t>Dr. P. Srinivasan</t>
   </si>
   <si>
     <t>Dr. Sachin U Belgamwar</t>
-  </si>
-  <si>
-    <t>Hemant Sharma</t>
-  </si>
-  <si>
-    <t>Srinibas Tripathy</t>
   </si>
   <si>
     <t>Management</t>
@@ -1103,7 +1103,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m-d"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1114,6 +1117,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF0E0E0E"/>
+      <name val="Nunito Sans"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <u/>
@@ -1147,17 +1158,29 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -2610,6 +2633,7 @@
       <c r="A255" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="B255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" s="1" t="s">
@@ -2831,428 +2855,451 @@
         <v>285</v>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
     <row r="302">
-      <c r="A302" s="1" t="s">
-        <v>286</v>
+      <c r="A302" s="5" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="s">
-        <v>287</v>
+      <c r="A303" s="5" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="s">
-        <v>255</v>
-      </c>
+      <c r="A304" s="1"/>
     </row>
     <row r="305">
       <c r="A305" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="s">
-        <v>290</v>
+      <c r="A307" s="6" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="1" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="3" t="s">
-        <v>324</v>
+      <c r="A344" s="1" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="7" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="1" t="s">
+      <c r="A349" s="1" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="s">
-        <v>285</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="7" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="s">
-        <v>330</v>
+        <v>287</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" s="1" t="s">
-        <v>245</v>
+        <v>285</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="s">
-        <v>249</v>
+        <v>332</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="s">
-        <v>294</v>
+        <v>333</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="1" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
-        <v>334</v>
+        <v>293</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="1" t="s">
-        <v>336</v>
+        <v>294</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="1" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="s">
         <v>361</v>
       </c>
     </row>

--- a/server/scripts/professors.xlsx
+++ b/server/scripts/professors.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="363">
   <si>
     <t>CSIS</t>
   </si>
@@ -881,6 +881,9 @@
   </si>
   <si>
     <t>Srinibas Tripathy</t>
+  </si>
+  <si>
+    <t>Sunil Sinhmar</t>
   </si>
   <si>
     <t>Civil</t>
@@ -2876,12 +2879,12 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1"/>
+      <c r="A304" s="1" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="s">
-        <v>290</v>
-      </c>
+      <c r="A305" s="1"/>
     </row>
     <row r="306">
       <c r="A306" s="1" t="s">
@@ -2889,13 +2892,13 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="6" t="s">
+      <c r="A307" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="6" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="309">
@@ -2928,8 +2931,8 @@
         <v>298</v>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" s="1" t="s">
+    <row r="315">
+      <c r="A315" s="1" t="s">
         <v>299</v>
       </c>
     </row>
@@ -2983,8 +2986,8 @@
         <v>309</v>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" s="1" t="s">
+    <row r="327">
+      <c r="A327" s="1" t="s">
         <v>310</v>
       </c>
     </row>
@@ -3058,8 +3061,8 @@
         <v>324</v>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" s="1" t="s">
+    <row r="343">
+      <c r="A343" s="1" t="s">
         <v>325</v>
       </c>
     </row>
@@ -3074,13 +3077,13 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="7" t="s">
+      <c r="A347" s="1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="7" t="s">
         <v>286</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" s="1" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="349">
@@ -3088,29 +3091,29 @@
         <v>329</v>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" s="1" t="s">
+    <row r="350">
+      <c r="A350" s="1" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="7" t="s">
+      <c r="A352" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="s">
-        <v>287</v>
+      <c r="A353" s="7" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="357">
@@ -3120,37 +3123,37 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="s">
-        <v>245</v>
+        <v>334</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="365">
@@ -3158,9 +3161,9 @@
         <v>294</v>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" s="1" t="s">
-        <v>334</v>
+    <row r="366">
+      <c r="A366" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="368">
@@ -3180,12 +3183,12 @@
     </row>
     <row r="371">
       <c r="A371" s="1" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
     </row>
     <row r="373">
@@ -3208,8 +3211,8 @@
         <v>342</v>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" s="1" t="s">
+    <row r="377">
+      <c r="A377" s="1" t="s">
         <v>343</v>
       </c>
     </row>
@@ -3301,6 +3304,11 @@
     <row r="396">
       <c r="A396" s="1" t="s">
         <v>361</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
